--- a/tests/resources/EVA_Submission_test_fails.xlsx
+++ b/tests/resources/EVA_Submission_test_fails.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB326402-F572-F144-AB92-DE4D7D92AE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16500" yWindow="-28200" windowWidth="51200" windowHeight="28200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLEASE READ FIRST" sheetId="1" r:id="rId1"/>
@@ -2415,11 +2415,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2433,14 +2439,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2448,14 +2448,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2754,10 +2754,10 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="72"/>
+      <c r="B2" s="74"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2766,10 +2766,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="75" t="s">
         <v>598</v>
       </c>
-      <c r="B3" s="73"/>
+      <c r="B3" s="75"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2778,10 +2778,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="74"/>
+      <c r="B4" s="76"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2790,10 +2790,10 @@
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="75"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4870,10 +4870,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="77"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6926,10 +6926,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="78"/>
+      <c r="B11" s="73"/>
     </row>
     <row r="12" spans="1:1025" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -6989,28 +6989,28 @@
       </c>
     </row>
     <row r="20" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="76"/>
+      <c r="B20" s="70"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="76"/>
+      <c r="B21" s="70"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="76"/>
+      <c r="B22" s="70"/>
     </row>
     <row r="23" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="76"/>
+      <c r="B23" s="70"/>
     </row>
     <row r="24" spans="1:1025" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
@@ -8042,6 +8042,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="3qY1zXOukEGJGo1D3KFTAIEoR11Js5sQl8rVnJc99Ney+BRNSoCe82WsvGSKwnyGZMiibV4N6XXWiSqA0A4S8A==" saltValue="IV+DQNr8g9d19NNKzBaBew==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
@@ -8050,11 +8055,6 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9930,10 +9930,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="78" t="s">
         <v>593</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="78"/>
     </row>
     <row r="2" spans="1:2" s="66" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
@@ -11070,10 +11070,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="83"/>
       <c r="C1" s="79"/>
       <c r="D1" s="43" t="s">
         <v>217</v>
@@ -11139,16 +11139,16 @@
       <c r="I2" s="82"/>
       <c r="J2" s="82"/>
       <c r="K2" s="82"/>
-      <c r="L2" s="83" t="s">
+      <c r="L2" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83" t="s">
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
       <c r="R2" s="82" t="s">
         <v>151</v>
       </c>
@@ -11380,16 +11380,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="Z2:AI2"/>
     <mergeCell ref="AJ2:AS2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:N2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Metadata and VCF" prompt="These sample names must match those provided in the VCF file(s)" sqref="E1 B4:B1003" xr:uid="{00000000-0002-0000-0700-000000000000}">
